--- a/app/static/template.xlsx
+++ b/app/static/template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t xml:space="preserve">Matrice NOM DU PROJET</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t xml:space="preserve">Pourquoi avoir choisi ce composant ? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pourquoi avoir avoir choisi ce produit ? </t>
   </si>
   <si>
     <t xml:space="preserve">Conforme</t>
@@ -169,7 +166,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="16">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -271,13 +268,6 @@
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right/>
       <top style="medium"/>
       <bottom style="medium"/>
       <diagonal/>
@@ -315,7 +305,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -416,10 +406,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -432,7 +418,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -901,128 +887,33 @@
       <c r="H13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0"/>
-      <c r="C14" s="0"/>
-      <c r="D14" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="0"/>
-      <c r="G14" s="0"/>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0"/>
-      <c r="C15" s="0"/>
-      <c r="D15" s="0"/>
-      <c r="E15" s="0"/>
-      <c r="F15" s="0"/>
-      <c r="G15" s="0"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0"/>
-      <c r="C16" s="0"/>
-      <c r="D16" s="0"/>
-      <c r="E16" s="0"/>
-      <c r="F16" s="0"/>
-      <c r="G16" s="0"/>
+      <c r="D14" s="0"/>
+      <c r="E14" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0"/>
-      <c r="C17" s="0"/>
-      <c r="D17" s="0"/>
-      <c r="E17" s="0"/>
-      <c r="F17" s="0"/>
-      <c r="G17" s="0"/>
       <c r="H17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0"/>
-      <c r="C18" s="0"/>
-      <c r="D18" s="0"/>
-      <c r="E18" s="0"/>
-      <c r="F18" s="0"/>
-      <c r="G18" s="0"/>
       <c r="H18" s="24"/>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0"/>
-      <c r="C19" s="0"/>
-      <c r="D19" s="0"/>
-      <c r="E19" s="0"/>
-      <c r="F19" s="0"/>
-      <c r="G19" s="0"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0"/>
-      <c r="C20" s="0"/>
-      <c r="D20" s="0"/>
-      <c r="E20" s="0"/>
-      <c r="F20" s="0"/>
-      <c r="G20" s="0"/>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0"/>
-      <c r="C21" s="0"/>
-      <c r="D21" s="0"/>
-      <c r="E21" s="0"/>
-      <c r="F21" s="0"/>
-      <c r="G21" s="0"/>
-    </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="0"/>
-      <c r="C22" s="0"/>
-      <c r="D22" s="0"/>
-      <c r="E22" s="0"/>
-      <c r="F22" s="0"/>
-      <c r="G22" s="0"/>
       <c r="H22" s="24"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0"/>
-      <c r="C23" s="0"/>
-      <c r="D23" s="0"/>
-      <c r="E23" s="0"/>
-      <c r="F23" s="0"/>
-      <c r="G23" s="0"/>
       <c r="H23" s="24"/>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0"/>
-      <c r="C24" s="0"/>
-      <c r="D24" s="0"/>
-      <c r="E24" s="0"/>
-      <c r="F24" s="0"/>
-      <c r="G24" s="0"/>
-    </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="0"/>
-      <c r="C25" s="0"/>
-      <c r="D25" s="0"/>
-      <c r="E25" s="0"/>
-      <c r="F25" s="0"/>
-      <c r="G25" s="0"/>
       <c r="H25" s="24"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0"/>
-      <c r="C26" s="0"/>
-      <c r="D26" s="0"/>
-      <c r="E26" s="0"/>
-      <c r="F26" s="0"/>
-      <c r="G26" s="0"/>
       <c r="H26" s="24"/>
     </row>
-    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D27" s="0"/>
-      <c r="E27" s="0"/>
-    </row>
+    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E39" s="26"/>
+      <c r="E39" s="25"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E51" s="26"/>
+      <c r="E51" s="25"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1036,7 +927,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{C2416619-562B-497C-8B41-8DF085AB64C9}">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{A65D46E1-23D2-41F4-8FCA-E974AAEC38B2}">
             <xm:f>"PC"</xm:f>
             <x14:dxf>
               <fill>
@@ -1046,7 +937,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{6A9AD114-EF7E-49F9-BB37-D5975869EE6A}">
+          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{5E981FF7-E11B-4E88-BB00-81577DC9902F}">
             <xm:f>"C"</xm:f>
             <x14:dxf>
               <fill>
@@ -1056,7 +947,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{522CF061-516A-47B4-9280-B800C6BB8EA2}">
+          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{B099851B-9AB1-4EE0-A644-93416E471E6D}">
             <xm:f>"NC"</xm:f>
             <x14:dxf>
               <fill>
@@ -1066,10 +957,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E13:E14 E28:E30</xm:sqref>
+          <xm:sqref>E13 E28:E30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{C46BC346-602C-4FD4-8198-BF1F5BDFC28A}">
+          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{A7B1B0E8-48F7-4C98-8077-1FF5CA172323}">
             <xm:f>"PC"</xm:f>
             <x14:dxf>
               <fill>
@@ -1079,7 +970,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{BFEE6932-C3B4-4691-9DAA-3E563B638B7C}">
+          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{506049E5-CE37-4186-A9A2-A4ACEE24E740}">
             <xm:f>"C"</xm:f>
             <x14:dxf>
               <fill>
@@ -1089,7 +980,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{75A89684-115C-47EA-9250-C34B4F63B4D2}">
+          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{7C7B6753-8DA5-4BA2-8BFA-CC6F13EC8B6C}">
             <xm:f>"NC"</xm:f>
             <x14:dxf>
               <fill>
@@ -1102,7 +993,7 @@
           <xm:sqref>F13 F27:F30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{3F77C090-4AD2-4A40-BB20-58306616E3CE}">
+          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{4BA0A6D4-4FB6-4CBB-9092-F716F14D7E4E}">
             <xm:f>"PC"</xm:f>
             <x14:dxf>
               <fill>
@@ -1112,7 +1003,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{B3EAD726-EDDB-4A9C-B0C3-54F6A97968D2}">
+          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{BB83805D-EC23-437A-9AA0-65703B7ECDE5}">
             <xm:f>"C"</xm:f>
             <x14:dxf>
               <fill>
@@ -1122,7 +1013,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="10" operator="equal" id="{3EA3FCE0-10A1-422F-9D42-7276E0B0329E}">
+          <x14:cfRule type="cellIs" priority="10" operator="equal" id="{74CAB229-9DD9-4378-93EC-68B2725942C0}">
             <xm:f>"NC"</xm:f>
             <x14:dxf>
               <fill>
@@ -1135,7 +1026,7 @@
           <xm:sqref>E5:E7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="11" operator="equal" id="{1092BCD5-37A3-4FA7-9893-759F446FBB4D}">
+          <x14:cfRule type="cellIs" priority="11" operator="equal" id="{40E11653-593A-49A5-B04C-E22695C9118C}">
             <xm:f>"PC"</xm:f>
             <x14:dxf>
               <fill>
@@ -1145,7 +1036,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="12" operator="equal" id="{8EBDC7F4-80BF-4370-9298-E631E3D9F16E}">
+          <x14:cfRule type="cellIs" priority="12" operator="equal" id="{2DBCE01B-C0F2-4E96-A7DE-DF503CA5B697}">
             <xm:f>"C"</xm:f>
             <x14:dxf>
               <fill>
@@ -1155,7 +1046,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="13" operator="equal" id="{6E66E9C4-835B-4C89-B15E-7EF0584F3E6B}">
+          <x14:cfRule type="cellIs" priority="13" operator="equal" id="{C7DA852C-655A-4BC5-82C6-427DA988E1D9}">
             <xm:f>"NC"</xm:f>
             <x14:dxf>
               <fill>
@@ -1182,33 +1073,33 @@
   <sheetFormatPr defaultColWidth="10.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="28" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="28" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="29"/>
+      <c r="C7" s="27" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="30"/>
-      <c r="C7" s="28" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1114,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{FA8CB6ED-CDFD-4E4C-AA7A-F4EBBA8B88C3}">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{5CEF4C69-FF4E-41D3-A769-9A2896872A91}">
             <xm:f>"PC"</xm:f>
             <x14:dxf>
               <fill>
@@ -1233,7 +1124,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{B2E5BE3A-1FAA-4C91-9E2B-8D99B5603213}">
+          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{D6838AC2-C01D-4CDB-BCE1-3EB826E7ECF0}">
             <xm:f>"C"</xm:f>
             <x14:dxf>
               <fill>
@@ -1243,7 +1134,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{B054E0C9-C42C-497F-8FC4-6255E71A20E3}">
+          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{1F7A3012-DFE0-4142-82B1-98B0649DD687}">
             <xm:f>"NC"</xm:f>
             <x14:dxf>
               <fill>
